--- a/output/pdf_financials_xlsx/CGNT.xlsx
+++ b/output/pdf_financials_xlsx/CGNT.xlsx
@@ -1219,31 +1219,31 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.463798</v>
+        <v>-0.463798</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.310454</v>
+        <v>-1.310454</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.168072</v>
+        <v>-1.168072</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.439265</v>
+        <v>-1.439265</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.579875</v>
+        <v>-0.579875</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.042112</v>
+        <v>-0.042112</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.08741</v>
+        <v>-0.08741</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.320261</v>
+        <v>-0.320261</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.495387</v>
+        <v>-0.495387</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0.350299</v>
@@ -1264,7 +1264,7 @@
         <v>8.364373000000001</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>15.800268</v>
+        <v>-15.800268</v>
       </c>
     </row>
     <row r="17">
@@ -1301,22 +1301,22 @@
         <v>-0</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.7005980000000001</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.509524</v>
+        <v>-7.747272</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.496072</v>
+        <v>-20.774454</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0.1264</v>
+        <v>-15.277424</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0.1264</v>
+        <v>-15.277424</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>-0</v>
+        <v>-16.728746</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>-0</v>
@@ -1503,52 +1503,52 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.463798</v>
+        <v>-0.463798</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.310454</v>
+        <v>-1.310454</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.168072</v>
+        <v>-1.168072</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.439265</v>
+        <v>-1.439265</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.579875</v>
+        <v>-0.579875</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.042112</v>
+        <v>-0.042112</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.08741</v>
+        <v>-0.08741</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.320261</v>
+        <v>-0.320261</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.495387</v>
+        <v>-0.495387</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.350299</v>
+        <v>-0.350299</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.618874</v>
+        <v>-3.618874</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>10.139191</v>
+        <v>-10.139191</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>7.575512</v>
+        <v>-7.575512</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>7.575512</v>
+        <v>-7.575512</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>8.364373000000001</v>
+        <v>-8.364373000000001</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>15.800268</v>
+        <v>-15.800268</v>
       </c>
     </row>
     <row r="21">
@@ -1668,52 +1668,52 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.463798</v>
+        <v>-0.463798</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.310454</v>
+        <v>-1.310454</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.168072</v>
+        <v>-1.168072</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.439265</v>
+        <v>-1.439265</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.579875</v>
+        <v>-0.579875</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.042112</v>
+        <v>-0.042112</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.08741</v>
+        <v>-0.08741</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.320261</v>
+        <v>-0.320261</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.495387</v>
+        <v>-0.495387</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.350299</v>
+        <v>-0.350299</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.618874</v>
+        <v>-3.618874</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>10.139191</v>
+        <v>-10.139191</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>7.575512</v>
+        <v>-7.575512</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>7.575512</v>
+        <v>-7.575512</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>8.364373000000001</v>
+        <v>-8.364373000000001</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>15.800268</v>
+        <v>-15.800268</v>
       </c>
     </row>
     <row r="24">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>15.459933</v>
+        <v>-15.459933</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>18.720771</v>
+        <v>-18.720771</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1895,22 +1895,22 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>72.37748000000001</v>
+        <v>-72.37748000000001</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-44.083439</v>
+        <v>44.083439</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>11.306734</v>
+        <v>-11.306734</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>11.306734</v>
+        <v>-11.306734</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-44.023016</v>
+        <v>44.023016</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>-98.75167500000001</v>
+        <v>98.75167500000001</v>
       </c>
     </row>
     <row r="27">
@@ -1920,31 +1920,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.463798</v>
+        <v>-0.463798</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.310454</v>
+        <v>-1.310454</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.168072</v>
+        <v>-1.168072</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.439265</v>
+        <v>-1.439265</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.579875</v>
+        <v>-0.579875</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.042112</v>
+        <v>-0.042112</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.08741</v>
+        <v>-0.08741</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.320261</v>
+        <v>-0.320261</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.495387</v>
+        <v>-0.495387</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.350299</v>
@@ -1965,7 +1965,7 @@
         <v>8.364373000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>15.800268</v>
+        <v>-15.800268</v>
       </c>
     </row>
     <row r="28">
@@ -2030,31 +2030,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.463798</v>
+        <v>-0.463798</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.310454</v>
+        <v>-1.310454</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.168072</v>
+        <v>-1.168072</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.44304</v>
+        <v>-1.43549</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.5820109999999999</v>
+        <v>-0.577739</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.042112</v>
+        <v>-0.042112</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.08741</v>
+        <v>-0.08741</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.320261</v>
+        <v>-0.320261</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.495387</v>
+        <v>-0.495387</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.350646</v>
@@ -2075,7 +2075,7 @@
         <v>8.527668</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>15.800268</v>
+        <v>-15.800268</v>
       </c>
     </row>
     <row r="30">
@@ -2172,52 +2172,52 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>12.34193021118603</v>
+        <v>187.658069788814</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>4.664407452829328</v>
+        <v>195.3355925471707</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>1.64115092460158</v>
+        <v>198.3588490753984</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>1.64115092460158</v>
+        <v>198.3588490753984</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5606,16 +5606,16 @@
         <v>0.1125</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.153271</v>
+        <v>0.0075</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.172286</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.172286</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -5642,13 +5642,13 @@
         <v>8.338169000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.641629</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>15.824323</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>22.378961</v>
       </c>
     </row>
     <row r="93">
@@ -9886,7 +9886,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -11130,7 +11134,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -13134,7 +13142,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -16900,7 +16912,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -17958,7 +17974,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -19008,7 +19028,11 @@
           <t>Warrants reserve (note 10)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -20170,7 +20194,11 @@
           <t>Warrants reserve (note 8) -</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -42665,13 +42693,13 @@
         </is>
       </c>
       <c r="R365" s="5" t="n">
-        <v>7.575512</v>
+        <v>-7.575512</v>
       </c>
       <c r="S365" s="5" t="n">
-        <v>8.364373000000001</v>
+        <v>-8.364373000000001</v>
       </c>
       <c r="T365" s="5" t="n">
-        <v>15.800268</v>
+        <v>-15.800268</v>
       </c>
     </row>
     <row r="366">
@@ -42853,13 +42881,13 @@
         </is>
       </c>
       <c r="R367" s="5" t="n">
-        <v>7.565692</v>
+        <v>-7.565692</v>
       </c>
       <c r="S367" s="5" t="n">
-        <v>8.379899</v>
+        <v>-8.379899</v>
       </c>
       <c r="T367" s="5" t="n">
-        <v>15.874525</v>
+        <v>-15.874525</v>
       </c>
     </row>
     <row r="368">
@@ -48096,10 +48124,10 @@
         </is>
       </c>
       <c r="Q422" s="5" t="n">
-        <v>7.575512</v>
+        <v>-7.575512</v>
       </c>
       <c r="R422" s="5" t="n">
-        <v>13.726057</v>
+        <v>-13.726057</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
@@ -48244,10 +48272,10 @@
         </is>
       </c>
       <c r="I424" s="5" t="n">
-        <v>0.577562</v>
+        <v>-0.577562</v>
       </c>
       <c r="J424" s="5" t="n">
-        <v>0.042112</v>
+        <v>-0.042112</v>
       </c>
       <c r="K424" t="inlineStr">
         <is>
@@ -48275,13 +48303,13 @@
         </is>
       </c>
       <c r="P424" s="5" t="n">
-        <v>10.133495</v>
+        <v>-10.133495</v>
       </c>
       <c r="Q424" s="5" t="n">
-        <v>7.565692</v>
+        <v>-7.565692</v>
       </c>
       <c r="R424" s="5" t="n">
-        <v>13.667968</v>
+        <v>-13.667968</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -51033,10 +51061,10 @@
         </is>
       </c>
       <c r="P453" s="5" t="n">
-        <v>10.139191</v>
+        <v>-10.139191</v>
       </c>
       <c r="Q453" s="5" t="n">
-        <v>13.726057</v>
+        <v>-13.726057</v>
       </c>
       <c r="R453" t="inlineStr">
         <is>
@@ -51961,10 +51989,10 @@
         </is>
       </c>
       <c r="N463" s="5" t="n">
-        <v>0.350299</v>
+        <v>-0.350299</v>
       </c>
       <c r="O463" s="5" t="n">
-        <v>3.618874</v>
+        <v>-3.618874</v>
       </c>
       <c r="P463" t="inlineStr">
         <is>
@@ -53198,10 +53226,10 @@
         </is>
       </c>
       <c r="M476" s="5" t="n">
-        <v>0.495387</v>
+        <v>-0.495387</v>
       </c>
       <c r="N476" s="5" t="n">
-        <v>0.350299</v>
+        <v>-0.350299</v>
       </c>
       <c r="O476" t="inlineStr">
         <is>
@@ -53949,10 +53977,10 @@
         </is>
       </c>
       <c r="L484" s="5" t="n">
-        <v>0.320261</v>
+        <v>-0.320261</v>
       </c>
       <c r="M484" s="5" t="n">
-        <v>0.495387</v>
+        <v>-0.495387</v>
       </c>
       <c r="N484" t="inlineStr">
         <is>
@@ -54322,10 +54350,10 @@
         </is>
       </c>
       <c r="K488" s="5" t="n">
-        <v>0.08741</v>
+        <v>-0.08741</v>
       </c>
       <c r="L488" s="5" t="n">
-        <v>0.320261</v>
+        <v>-0.320261</v>
       </c>
       <c r="M488" t="inlineStr">
         <is>
@@ -57462,10 +57490,10 @@
         </is>
       </c>
       <c r="I521" s="5" t="n">
-        <v>0.579875</v>
+        <v>-0.579875</v>
       </c>
       <c r="J521" s="5" t="n">
-        <v>0.042112</v>
+        <v>-0.042112</v>
       </c>
       <c r="K521" t="inlineStr">
         <is>
@@ -58494,13 +58522,13 @@
         </is>
       </c>
       <c r="G532" s="5" t="n">
-        <v>1.168072</v>
+        <v>-1.168072</v>
       </c>
       <c r="H532" s="5" t="n">
-        <v>1.439265</v>
+        <v>-1.439265</v>
       </c>
       <c r="I532" s="5" t="n">
-        <v>0.579875</v>
+        <v>-0.579875</v>
       </c>
       <c r="J532" t="inlineStr">
         <is>
@@ -58773,16 +58801,16 @@
         </is>
       </c>
       <c r="F535" s="5" t="n">
-        <v>1.309766</v>
+        <v>-1.309766</v>
       </c>
       <c r="G535" s="5" t="n">
-        <v>1.169395</v>
+        <v>-1.169395</v>
       </c>
       <c r="H535" s="5" t="n">
-        <v>1.438381</v>
+        <v>-1.438381</v>
       </c>
       <c r="I535" s="5" t="n">
-        <v>0.577562</v>
+        <v>-0.577562</v>
       </c>
       <c r="J535" t="inlineStr">
         <is>
@@ -59701,10 +59729,10 @@
         </is>
       </c>
       <c r="F545" s="5" t="n">
-        <v>1.310454</v>
+        <v>-1.310454</v>
       </c>
       <c r="G545" s="5" t="n">
-        <v>1.168072</v>
+        <v>-1.168072</v>
       </c>
       <c r="H545" t="inlineStr">
         <is>
@@ -60554,10 +60582,10 @@
         </is>
       </c>
       <c r="E554" s="5" t="n">
-        <v>0.463798</v>
+        <v>-0.463798</v>
       </c>
       <c r="F554" s="5" t="n">
-        <v>1.303315</v>
+        <v>-1.303315</v>
       </c>
       <c r="G554" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CGNT.xlsx
+++ b/output/pdf_financials_xlsx/CGNT.xlsx
@@ -922,7 +922,7 @@
         <v>4.112647</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.491486</v>
+        <v>11.360869</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>5.380626</v>
@@ -977,7 +977,7 @@
         <v>-4.112647</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-1.491486</v>
+        <v>-11.360869</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>-5.380626</v>
@@ -2321,16 +2321,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.186553</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.186553</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.610401</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.254803</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0.393617</v>
@@ -2363,10 +2363,10 @@
         <v>0.49375</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.99987</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>8.6275</v>
       </c>
     </row>
     <row r="35">
@@ -2431,16 +2431,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.186553</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.5</v>
+        <v>0.686553</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.610401</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.254803</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0.393617</v>
@@ -2473,10 +2473,10 @@
         <v>0.49375</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.99987</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>8.6275</v>
       </c>
     </row>
     <row r="37">
@@ -3094,13 +3094,13 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.151914</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.674727</v>
+        <v>0.06432599999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.292544</v>
+        <v>0.037741</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.007713</v>
@@ -3133,10 +3133,10 @@
         <v>0.08601300000000001</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.444133</v>
+        <v>0.444263</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>9.052963999999999</v>
+        <v>0.425464</v>
       </c>
     </row>
     <row r="49">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -50424,7 +50424,7 @@
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">

--- a/output/pdf_financials_xlsx/CGNT.xlsx
+++ b/output/pdf_financials_xlsx/CGNT.xlsx
@@ -1304,13 +1304,13 @@
         <v>-0.7005980000000001</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-7.747272</v>
+        <v>0.509524</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-20.774454</v>
+        <v>0.496072</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-15.277424</v>
+        <v>0.347172</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-15.277424</v>
@@ -2202,13 +2202,13 @@
         <v>200</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>187.658069788814</v>
+        <v>12.34193021118603</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>195.3355925471707</v>
+        <v>4.664407452829328</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>198.3588490753984</v>
+        <v>4.507607980979269</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>198.3588490753984</v>
@@ -4207,10 +4207,10 @@
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.420743</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.195641</v>
       </c>
       <c r="O67" s="3" t="n">
         <v>0</v>
@@ -6611,7 +6611,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.032548</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -6861,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.11317</v>
       </c>
       <c r="P115" s="3" t="n">
         <v>0</v>
@@ -7928,7 +7928,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.032548</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
         <v>-1.200189</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-1.195487</v>
+        <v>-1.228035</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>-0.502587</v>
@@ -25476,7 +25476,11 @@
           <t>Warrants exercised during the private placement</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -28780,7 +28784,11 @@
           <t>Proceeds from sale of marketable securities 6</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -30216,7 +30224,11 @@
           <t>Deferred income tax recovery 11</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -31616,7 +31628,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -34882,7 +34898,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>
@@ -37274,7 +37294,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -50906,7 +50930,11 @@
           <t>12 Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -51842,7 +51870,11 @@
           <t>10,11 Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
